--- a/TestData/Opencart_LoginData.xlsx
+++ b/TestData/Opencart_LoginData.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\Desktop\Java selenium-resource\Hybrid Framework\Day 51\Part6-Login+Data+Driven+Test\Part6-Login Data Driven Test\testData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\arpan\eclipse-workspace\Hybrid_OpenCart_Framework\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A9DA2DB-10B8-4101-A166-3B53A1FE2252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FB6C75-CC6A-493B-BFE4-28B86DC872FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{1F2D179E-37D2-4BC0-88A9-F5C135B87DA5}"/>
   </bookViews>
@@ -39,15 +39,9 @@
     <t>lakshmi@yahoo.com</t>
   </si>
   <si>
-    <t>Lakshmi</t>
-  </si>
-  <si>
     <t>Valid</t>
   </si>
   <si>
-    <t>laksh@yahoo.com</t>
-  </si>
-  <si>
     <t>Laxmi</t>
   </si>
   <si>
@@ -60,20 +54,26 @@
     <t>xyz</t>
   </si>
   <si>
-    <t>pavanoltraining@gmail.com</t>
-  </si>
-  <si>
     <t>test@123</t>
   </si>
   <si>
     <t>abc123@gmail.com</t>
+  </si>
+  <si>
+    <t>sfvefvte@gmail.com</t>
+  </si>
+  <si>
+    <t>abc@xyz</t>
+  </si>
+  <si>
+    <t>newproject2@xyz.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -82,24 +82,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="16"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -143,27 +127,19 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -500,67 +476,66 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>4</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>8</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="21" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>5</v>
+        <v>10</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" xr:uid="{D3BE7519-95C3-4ACD-9AB4-5385C9508082}"/>
-    <hyperlink ref="A4" r:id="rId2" xr:uid="{8456409A-CACC-4B7E-B78E-75E713148E0E}"/>
-    <hyperlink ref="A3" r:id="rId3" xr:uid="{5E52A498-5B14-4BDC-BBF1-05425B8AC197}"/>
-    <hyperlink ref="A5" r:id="rId4" xr:uid="{94E9D5A6-98A1-4A25-BDDE-C5B20EDA887E}"/>
-    <hyperlink ref="B2" r:id="rId5" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
-    <hyperlink ref="A6" r:id="rId6" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
-    <hyperlink ref="B6" r:id="rId7" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
+    <hyperlink ref="A3" r:id="rId2" xr:uid="{5E52A498-5B14-4BDC-BBF1-05425B8AC197}"/>
+    <hyperlink ref="A5" r:id="rId3" xr:uid="{94E9D5A6-98A1-4A25-BDDE-C5B20EDA887E}"/>
+    <hyperlink ref="B2" r:id="rId4" xr:uid="{968262D0-AE14-41EF-AB8A-08B3F886E797}"/>
+    <hyperlink ref="A6" r:id="rId5" xr:uid="{75A4F8D6-7BF1-446B-9367-475FA4FB44C7}"/>
+    <hyperlink ref="B6" r:id="rId6" xr:uid="{01D5649A-5E55-45E1-9B81-1CE430C208A1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId8"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId7"/>
 </worksheet>
 </file>